--- a/college-posters/data/字段表_第一批.xlsx
+++ b/college-posters/data/字段表_第一批.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -505,17 +505,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2025届本科毕业生深造率75.05%（媒体转述）；本科生出国（境）深造17.3%（清华官方）；另有口径“本科升学占比54.10%”，差异较大</t>
+          <t>国家重要领域重点单位、高端制造与能源、信息技术与互联网</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>待核报告原文（口径不一）</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -527,17 +527,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>国家重要领域重点单位、高端制造与能源、信息技术与互联网</t>
+          <t>二校门：清华园标志，始建于1909年；大礼堂：清华早期四大建筑之一；荷塘：朱自清《荷塘月色》所写之地</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -549,39 +549,39 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>二校门：清华园标志，始建于1909年；大礼堂：清华早期四大建筑之一；荷塘：朱自清《荷塘月色》所写之地</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>北京大学</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>数学与应用数学、物理学、汉语言文学、经济学、法学、临床医学</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -593,17 +593,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>数学与应用数学、物理学、汉语言文学、经济学、法学、临床医学</t>
+          <t>科研院所与高校、金融与咨询、党政机关与国企</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -615,17 +615,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>科研院所与高校、金融与咨询、党政机关与国企</t>
+          <t>未名湖：燕园核心景观，钱穆命名；博雅塔：与湖、图书馆合称一塔湖图；西门：燕园正门，古典宫殿式</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -637,39 +637,39 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>未名湖：燕园核心景观，钱穆命名；博雅塔：与湖、图书馆合称一塔湖图；西门：燕园正门，古典宫殿式</t>
+          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>浙江大学</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>计算机科学与技术、软件工程、自动化、电气工程及其自动化、光电信息科学与工程、临床医学</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -681,17 +681,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术、软件工程、自动化、电气工程及其自动化、光电信息科学与工程、临床医学</t>
+          <t>互联网与数字经济、高端制造与能源、科研院所与高校</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -703,17 +703,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>互联网与数字经济、高端制造与能源、科研院所与高校</t>
+          <t>之江校区：之江大学旧址，国家级文保；启真湖：紫金港校区中心湖；玉泉校区：依老和山而建的老校区</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -725,39 +725,39 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>之江校区：之江大学旧址，国家级文保；启真湖：紫金港校区中心湖；玉泉校区：依老和山而建的老校区</t>
+          <t>理工医农类：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浙江大学</t>
+          <t>上海交通大学</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>第4张排名卡</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>理工医农类：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>第二轮双一流建设学科约18个（第三方逐项计数）</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核教育部名单原文</t>
         </is>
       </c>
     </row>
@@ -769,17 +769,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>第4张排名卡</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科约18个（第三方逐项计数）</t>
+          <t>船舶与海洋工程、机械工程、电子信息类、计算机科学与技术、临床医学、工商管理</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>待核教育部名单原文</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -791,17 +791,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>船舶与海洋工程、机械工程、电子信息类、计算机科学与技术、临床医学、工商管理</t>
+          <t>先进制造与能源、信息技术与互联网、金融与咨询</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>先进制造与能源、信息技术与互联网、金融与咨询</t>
+          <t>老图书馆：徐汇百年红砖楼，国家级文保；饮水思源碑：校训出处，校友捐建；钱学森图书馆：展示钱学森生平事迹</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -835,39 +835,39 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>老图书馆：徐汇百年红砖楼，国家级文保；饮水思源碑：校训出处，校友捐建；钱学森图书馆：展示钱学森生平事迹</t>
+          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>复旦大学</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>第4张排名卡</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>第二轮双一流建设学科约20个（第三方逐项计数）</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核教育部名单原文</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>第4张排名卡</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科约20个（第三方逐项计数）</t>
+          <t>新闻学、经济学、数学与应用数学、微电子科学与工程、临床医学、哲学</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核教育部名单原文</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -901,17 +901,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>新闻学、经济学、数学与应用数学、微电子科学与工程、临床医学、哲学</t>
+          <t>截至2024年8月，选择继续深造的学生占毕业生总数74.7%；2024届本科初次就业率90.23%</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核报告原文（是否仅本科口径）</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>截至2024年8月，选择继续深造的学生占毕业生总数74.7%；2024届本科初次就业率90.23%</t>
+          <t>金融与咨询、互联网与传媒、医疗卫生与科研</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>待核报告原文（是否仅本科口径）</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -945,17 +945,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>知名校友</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>金融与咨询、互联网与传媒、医疗卫生与科研</t>
+          <t>陈寅恪（1907年就读复旦公学）；闻玉梅（1956年上海第一医学院，现复旦上医）；吴晓波（1990年复旦新闻系）</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核（闻玉梅、陈寅恪就读经历）</t>
         </is>
       </c>
     </row>
@@ -967,17 +967,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>陈寅恪（1907年就读复旦公学）；闻玉梅（1956年上海第一医学院，现复旦上医）；吴晓波（1990年复旦新闻系）</t>
+          <t>光华楼：邯郸校区地标双子楼；相辉堂：纪念马相伯、李登辉两位校长；燕园：邯郸校区里的江南园林</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>待核（闻玉梅、陈寅恪就读经历）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -989,39 +989,39 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>光华楼：邯郸校区地标双子楼；相辉堂：纪念马相伯、李登辉两位校长；燕园：邯郸校区里的江南园林</t>
+          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>南京大学</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>第4张排名卡</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>第二轮双一流建设学科约16个（第三方逐项计数）</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核教育部名单原文</t>
         </is>
       </c>
     </row>
@@ -1033,17 +1033,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>第4张排名卡</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科约16个（第三方逐项计数）</t>
+          <t>天文学、地质学、物理学、化学、计算机科学与技术、汉语言文学</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>待核教育部名单原文</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -1055,17 +1055,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>天文学、地质学、物理学、化学、计算机科学与技术、汉语言文学</t>
+          <t>科研院所与高校、电子信息与互联网、党政机关与国企</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1077,17 +1077,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>知名校友</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>科研院所与高校、电子信息与互联网、党政机关与国企</t>
+          <t>吴健雄（1934年国立中央大学物理系）；冯康（1944年中央大学）；余光中（1947年就读金陵大学外文系）</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核（冯康、余光中学籍）</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>吴健雄（1934年国立中央大学物理系）；冯康（1944年中央大学）；余光中（1947年就读金陵大学外文系）</t>
+          <t>北大楼：鼓楼校区原金陵大学钟楼；金陵大学旧址：全国重点文物保护单位；仙林校区：仙林大学城中的主校区</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>待核（冯康、余光中学籍）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1121,39 +1121,39 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>北大楼：鼓楼校区原金陵大学钟楼；金陵大学旧址：全国重点文物保护单位；仙林校区：仙林大学城中的主校区</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>南京大学</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>物理学、化学、数学与应用数学、计算机科学与技术、核工程与核技术、生物科学</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>物理学、化学、数学与应用数学、计算机科学与技术、核工程与核技术、生物科学</t>
+          <t>科研院所与高校、芯片与信息技术、高新技术企业</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1187,17 +1187,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>科研院所与高校、芯片与信息技术、高新技术企业</t>
+          <t>郭沫若广场：纪念首任校长郭沫若；眼镜湖：东区中心湖，形似眼镜；同步辐射实验室：国家大科学装置</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1209,39 +1209,39 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>郭沫若广场：纪念首任校长郭沫若；眼镜湖：东区中心湖，形似眼镜；同步辐射实验室：国家大科学装置</t>
+          <t>中国科大绝大多数专业要求物理+化学</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>中国科学技术大学</t>
+          <t>武汉大学</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>中国科大绝大多数专业要求物理+化学</t>
+          <t>测绘工程、遥感科学与技术、法学、经济学、水利水电工程、口腔医学</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -1253,17 +1253,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>测绘工程、遥感科学与技术、法学、经济学、水利水电工程、口腔医学</t>
+          <t>2024届毕业生升学出国率约66%（片段，口径待确认）；2023届本科升学出国率接近60%</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核报告原文（数字来自片段）</t>
         </is>
       </c>
     </row>
@@ -1275,17 +1275,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>2024届毕业生升学出国率约66%（片段，口径待确认）；2023届本科升学出国率接近60%</t>
+          <t>电子信息与互联网、测绘遥感与水利电力、党政机关与国企</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>待核报告原文（数字来自片段）</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1297,17 +1297,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>电子信息与互联网、测绘遥感与水利电力、党政机关与国企</t>
+          <t>樱花城堡：老斋舍，每年三月樱花盛开；老图书馆：早期建筑群，国家级文保；珞珈山：依山傍湖的校园</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1319,39 +1319,39 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>樱花城堡：老斋舍，每年三月樱花盛开；老图书馆：早期建筑群，国家级文保；珞珈山：依山傍湖的校园</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>武汉大学</t>
+          <t>华中科技大学</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>机械设计制造及其自动化、电气工程及其自动化、光电信息科学与工程、计算机科学与技术、能源与动力工程、临床医学</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -1363,17 +1363,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>机械设计制造及其自动化、电气工程及其自动化、光电信息科学与工程、计算机科学与技术、能源与动力工程、临床医学</t>
+          <t>2023-2024学年本科教学质量报告：深造占已落实毕业去向人数的76.7%（分母为已落实去向，不是全部毕业生）</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核报告原文（口径特殊）</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2023-2024学年本科教学质量报告：深造占已落实毕业去向人数的76.7%（分母为已落实去向，不是全部毕业生）</t>
+          <t>电子信息与通信、先进制造与电力、医疗卫生</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>待核报告原文（口径特殊）</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1407,17 +1407,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>知名校友</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>电子信息与通信、先进制造与电力、医疗卫生</t>
+          <t>张小龙（华中理工大学电信系本科、硕士）；李培根（华中工学院校友、原校长）；骆清铭（华中理工大学光电校友）</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核（李培根、骆清铭学籍）</t>
         </is>
       </c>
     </row>
@@ -1429,17 +1429,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>张小龙（华中理工大学电信系本科、硕士）；李培根（华中工学院校友、原校长）；骆清铭（华中理工大学光电校友）</t>
+          <t>喻家山：主校区依山而建；森林校园：绿树成荫，有“森林大学”之称；南大门：华科标志性入口</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>待核（李培根、骆清铭学籍）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1451,39 +1451,39 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>喻家山：主校区依山而建；森林校园：绿树成荫，有“森林大学”之称；南大门：华科标志性入口</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>华中科技大学</t>
+          <t>西安交通大学</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>能源与动力工程、电气工程及其自动化、机械工程、核工程与核技术、计算机科学与技术、工商管理</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
@@ -1495,17 +1495,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>就业方向</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>能源与动力工程、电气工程及其自动化、机械工程、核工程与核技术、计算机科学与技术、工商管理</t>
+          <t>电力与能源、先进制造与国防、电子信息与互联网</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核就业质量报告</t>
         </is>
       </c>
     </row>
@@ -1517,17 +1517,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>电力与能源、先进制造与国防、电子信息与互联网</t>
+          <t>西迁纪念馆：讲述1956年交大西迁历史；樱花道：兴庆校区春日樱花大道；创新港：中国西部科技创新港</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -1539,37 +1539,15 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>西迁纪念馆：讲述1956年交大西迁历史；樱花道：兴庆校区春日樱花大道；创新港：中国西部科技创新港</t>
+          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>西安交通大学</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>待核2027年招生章程</t>
         </is>
@@ -3606,22 +3584,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2025届本科毕业生深造率75.05%（媒体转述）；本科生出国（境）深造17.3%（清华官方）；另有口径“本科升学占比54.10%”，差异较大</t>
+          <t>清华未公布本科整体深造率。海报改用官方数据：2025届毕业生国内重要领域重点单位就业率超86%（连续16年超80%）；本科生出国（境）深造17.3%。（第一批曾误用75.05%，经核实为同济大学2025届数据，已更正）</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>75.05%（2025届）</t>
+          <t>86%+（2025届毕业生）</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>清华新闻网、二级媒体转载</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>待核报告原文（口径不一）</t>
+          <t>清华新闻网转载中国青年报、清华官方微信</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>已核（口径为全体毕业生）</t>
         </is>
       </c>
     </row>

--- a/college-posters/data/字段表_第一批.xlsx
+++ b/college-posters/data/字段表_第一批.xlsx
@@ -1785,7 +1785,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9名</t>
+          <t>9名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>307名</t>
+          <t>307名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72名</t>
+          <t>72名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10名</t>
+          <t>10名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>296名</t>
+          <t>296名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79名</t>
+          <t>79名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1名</t>
+          <t>1名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14名</t>
+          <t>14名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18名</t>
+          <t>18名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2名</t>
+          <t>2名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13名</t>
+          <t>13名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22名</t>
+          <t>22名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3名</t>
+          <t>3名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>47名</t>
+          <t>47名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24名</t>
+          <t>24名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4名</t>
+          <t>4名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>36名</t>
+          <t>36名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27名</t>
+          <t>27名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5名</t>
+          <t>5名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26名</t>
+          <t>26名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41名</t>
+          <t>41名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6名</t>
+          <t>6名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>90名</t>
+          <t>90名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70名</t>
+          <t>70名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7名</t>
+          <t>7名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>134名</t>
+          <t>134名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39名</t>
+          <t>39名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8名</t>
+          <t>8名（2026）</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -8639,7 +8639,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>165名</t>
+          <t>165名（2027）</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77名</t>
+          <t>77名（2026）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">

--- a/college-posters/data/字段表_第一批.xlsx
+++ b/college-posters/data/字段表_第一批.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -505,68 +505,68 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>国家重要领域重点单位、高端制造与能源、信息技术与互联网</t>
+          <t>二校门：清华园标志，始建于1909年；大礼堂：清华早期四大建筑之一；荷塘：朱自清《荷塘月色》所写之地</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>北京大学</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>二校门：清华园标志，始建于1909年；大礼堂：清华早期四大建筑之一；荷塘：朱自清《荷塘月色》所写之地</t>
+          <t>数学与应用数学、物理学、汉语言文学、经济学、法学、临床医学</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>清华大学</t>
+          <t>北京大学</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>未名湖：燕园核心景观，钱穆命名；博雅塔：与湖、图书馆合称一塔湖图；西门：燕园正门，古典宫殿式</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>浙江大学</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>数学与应用数学、物理学、汉语言文学、经济学、法学、临床医学</t>
+          <t>计算机科学与技术、软件工程、自动化、电气工程及其自动化、光电信息科学与工程、临床医学</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -588,73 +588,73 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>浙江大学</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>科研院所与高校、金融与咨询、党政机关与国企</t>
+          <t>之江校区：之江大学旧址，国家级文保；启真湖：紫金港校区中心湖；玉泉校区：依老和山而建的老校区</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>上海交通大学</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>未名湖：燕园核心景观，钱穆命名；博雅塔：与湖、图书馆合称一塔湖图；西门：燕园正门，古典宫殿式</t>
+          <t>船舶与海洋工程、机械工程、电子信息类、计算机科学与技术、临床医学、工商管理</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>北京大学</t>
+          <t>上海交通大学</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>老图书馆：徐汇百年红砖楼，国家级文保；饮水思源碑：校训出处，校友捐建；钱学森图书馆：展示钱学森生平事迹</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浙江大学</t>
+          <t>复旦大学</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术、软件工程、自动化、电气工程及其自动化、光电信息科学与工程、临床医学</t>
+          <t>新闻学、经济学、数学与应用数学、微电子科学与工程、临床医学、哲学</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -676,29 +676,29 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浙江大学</t>
+          <t>复旦大学</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>互联网与数字经济、高端制造与能源、科研院所与高校</t>
+          <t>截至2024年8月，选择继续深造的学生占毕业生总数74.7%；2024届本科初次就业率90.23%</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核报告原文（是否仅本科口径）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浙江大学</t>
+          <t>复旦大学</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>之江校区：之江大学旧址，国家级文保；启真湖：紫金港校区中心湖；玉泉校区：依老和山而建的老校区</t>
+          <t>光华楼：邯郸校区地标双子楼；相辉堂：纪念马相伯、李登辉两位校长；燕园：邯郸校区里的江南园林</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -720,51 +720,51 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浙江大学</t>
+          <t>南京大学</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>理工医农类：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>天文学、地质学、物理学、化学、计算机科学与技术、汉语言文学</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>南京大学</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>第4张排名卡</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科约18个（第三方逐项计数）</t>
+          <t>北大楼：鼓楼校区原金陵大学钟楼；金陵大学旧址：全国重点文物保护单位；仙林校区：仙林大学城中的主校区</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>待核教育部名单原文</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>船舶与海洋工程、机械工程、电子信息类、计算机科学与技术、临床医学、工商管理</t>
+          <t>物理学、化学、数学与应用数学、计算机科学与技术、核工程与核技术、生物科学</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -786,770 +786,220 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>先进制造与能源、信息技术与互联网、金融与咨询</t>
+          <t>郭沫若广场：纪念首任校长郭沫若；眼镜湖：东区中心湖，形似眼镜；同步辐射实验室：国家大科学装置</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>中国科学技术大学</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>老图书馆：徐汇百年红砖楼，国家级文保；饮水思源碑：校训出处，校友捐建；钱学森图书馆：展示钱学森生平事迹</t>
+          <t>中国科大绝大多数专业要求物理+化学</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>上海交通大学</t>
+          <t>武汉大学</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>测绘工程、遥感科学与技术、法学、经济学、水利水电工程、口腔医学</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>武汉大学</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>第4张排名卡</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科约20个（第三方逐项计数）</t>
+          <t>2024届毕业生升学出国率约66%（片段，口径待确认）；2023届本科升学出国率接近60%</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核教育部名单原文</t>
+          <t>待核报告原文（数字来自片段）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>武汉大学</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>新闻学、经济学、数学与应用数学、微电子科学与工程、临床医学、哲学</t>
+          <t>樱花城堡：老斋舍，每年三月樱花盛开；老图书馆：早期建筑群，国家级文保；珞珈山：依山傍湖的校园</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>华中科技大学</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>深造率</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>截至2024年8月，选择继续深造的学生占毕业生总数74.7%；2024届本科初次就业率90.23%</t>
+          <t>机械设计制造及其自动化、电气工程及其自动化、光电信息科学与工程、计算机科学与技术、能源与动力工程、临床医学</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核报告原文（是否仅本科口径）</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>华中科技大学</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>深造率</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>金融与咨询、互联网与传媒、医疗卫生与科研</t>
+          <t>2023-2024学年本科教学质量报告：深造占已落实毕业去向人数的76.7%（分母为已落实去向，不是全部毕业生）</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核报告原文（口径特殊）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>华中科技大学</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>知名校友</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>陈寅恪（1907年就读复旦公学）；闻玉梅（1956年上海第一医学院，现复旦上医）；吴晓波（1990年复旦新闻系）</t>
+          <t>喻家山：主校区依山而建；森林校园：绿树成荫，有“森林大学”之称；南大门：华科标志性入口</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>待核（闻玉梅、陈寅恪就读经历）</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>西安交通大学</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>光华楼：邯郸校区地标双子楼；相辉堂：纪念马相伯、李登辉两位校长；燕园：邯郸校区里的江南园林</t>
+          <t>能源与动力工程、电气工程及其自动化、机械工程、核工程与核技术、计算机科学与技术、工商管理</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>复旦大学</t>
+          <t>西安交通大学</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>理工医类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>西迁纪念馆：讲述1956年交大西迁历史；樱花道：兴庆校区春日樱花大道；创新港：中国西部科技创新港</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>南京大学</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>第4张排名卡</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>第二轮双一流建设学科约16个（第三方逐项计数）</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>南京大学</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>天文学、地质学、物理学、化学、计算机科学与技术、汉语言文学</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>南京大学</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>科研院所与高校、电子信息与互联网、党政机关与国企</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>南京大学</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>知名校友</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>吴健雄（1934年国立中央大学物理系）；冯康（1944年中央大学）；余光中（1947年就读金陵大学外文系）</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>待核（冯康、余光中学籍）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>南京大学</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>北大楼：鼓楼校区原金陵大学钟楼；金陵大学旧址：全国重点文物保护单位；仙林校区：仙林大学城中的主校区</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
           <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>南京大学</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>中国科学技术大学</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>物理学、化学、数学与应用数学、计算机科学与技术、核工程与核技术、生物科学</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>中国科学技术大学</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>科研院所与高校、芯片与信息技术、高新技术企业</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>中国科学技术大学</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>郭沫若广场：纪念首任校长郭沫若；眼镜湖：东区中心湖，形似眼镜；同步辐射实验室：国家大科学装置</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>中国科学技术大学</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>中国科大绝大多数专业要求物理+化学</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>武汉大学</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>测绘工程、遥感科学与技术、法学、经济学、水利水电工程、口腔医学</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>武汉大学</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>深造率</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>2024届毕业生升学出国率约66%（片段，口径待确认）；2023届本科升学出国率接近60%</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>待核报告原文（数字来自片段）</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>武汉大学</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>电子信息与互联网、测绘遥感与水利电力、党政机关与国企</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>武汉大学</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>樱花城堡：老斋舍，每年三月樱花盛开；老图书馆：早期建筑群，国家级文保；珞珈山：依山傍湖的校园</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>武汉大学</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>华中科技大学</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>机械设计制造及其自动化、电气工程及其自动化、光电信息科学与工程、计算机科学与技术、能源与动力工程、临床医学</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>华中科技大学</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>深造率</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>2023-2024学年本科教学质量报告：深造占已落实毕业去向人数的76.7%（分母为已落实去向，不是全部毕业生）</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>待核报告原文（口径特殊）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>华中科技大学</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>电子信息与通信、先进制造与电力、医疗卫生</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>华中科技大学</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>知名校友</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>张小龙（华中理工大学电信系本科、硕士）；李培根（华中工学院校友、原校长）；骆清铭（华中理工大学光电校友）</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>待核（李培根、骆清铭学籍）</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>华中科技大学</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>喻家山：主校区依山而建；森林校园：绿树成荫，有“森林大学”之称；南大门：华科标志性入口</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>华中科技大学</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>西安交通大学</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>能源与动力工程、电气工程及其自动化、机械工程、核工程与核技术、计算机科学与技术、工商管理</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>西安交通大学</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>电力与能源、先进制造与国防、电子信息与互联网</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>西安交通大学</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>西迁纪念馆：讲述1956年交大西迁历史；樱花道：兴庆校区春日樱花大道；创新港：中国西部科技创新港</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>西安交通大学</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
@@ -2113,9 +1563,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2132,12 +1582,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>张小龙（华中理工大学电信系本科、硕士）；李培根（华中工学院校友、原校长）；骆清铭（华中理工大学光电校友）</t>
+          <t>张小龙（华中理工大学）；骆清铭（华中科技大学）；李培根本科学籍未核到，已撤下</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>张小龙 微信创始人；李培根 中国工程院院士；骆清铭 中国工程院院士</t>
+          <t>张小龙 微信创始人；骆清铭 中国工程院院士</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2145,9 +1595,9 @@
           <t>学校官网、权威媒体</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待核（李培根、骆清铭学籍）</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>已核（已更正）</t>
         </is>
       </c>
     </row>
@@ -2238,12 +1688,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -2871,9 +2321,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2996,12 +2446,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -3629,9 +3079,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3204,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4387,9 +3837,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -4512,12 +3962,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5145,9 +4595,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5270,12 +4720,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5116,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科约18个（第三方逐项计数）</t>
+          <t>第二轮双一流建设学科18个（理学4、工学9、医学4、哲社1）</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -5676,12 +5126,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>教育部 教研函〔2022〕1号 名单（转载）</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
+          <t>上海交大信息公开网</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>已核（学校官方）</t>
         </is>
       </c>
     </row>
@@ -5903,9 +5353,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6028,12 +5478,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -6424,7 +5874,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科约20个（第三方逐项计数）</t>
+          <t>第二轮双一流建设学科20个</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -6434,12 +5884,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>教育部 教研函〔2022〕1号 名单（转载）</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
+          <t>教育部附件节选逐项计数</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -6661,9 +6111,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6130,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>陈寅恪（1907年就读复旦公学）；闻玉梅（1956年上海第一医学院，现复旦上医）；吴晓波（1990年复旦新闻系）</t>
+          <t>陈寅恪（1907年插班考入复旦公学）；闻玉梅（1956年毕业于上海医学院，现复旦上医）；吴晓波（1990年复旦新闻系）</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -6693,9 +6143,9 @@
           <t>学校官网、权威媒体</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待核（闻玉梅、陈寅恪就读经历）</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -6786,12 +6236,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -7182,7 +6632,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>第二轮双一流建设学科约16个（第三方逐项计数）</t>
+          <t>第二轮双一流建设学科16个</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -7192,12 +6642,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>教育部 教研函〔2022〕1号 名单（转载）</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>待核教育部名单原文</t>
+          <t>科学网转载名单逐项计数</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -7419,9 +6869,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -7438,7 +6888,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>吴健雄（1934年国立中央大学物理系）；冯康（1944年中央大学）；余光中（1947年就读金陵大学外文系）</t>
+          <t>吴健雄（国立中央大学物理系）；冯康（1944年国立中央大学物理系毕业）；余光中（1947年考入金陵大学外文系）</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -7451,9 +6901,9 @@
           <t>学校官网、权威媒体</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>待核（冯康、余光中学籍）</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>已核</t>
         </is>
       </c>
     </row>
@@ -7544,12 +6994,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8177,9 +7627,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8302,7 +7752,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -8935,9 +8385,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -9060,12 +8510,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
